--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/order_items.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/order_items.xlsx
@@ -413,21 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
@@ -438,12 +443,15 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>101</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1001</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -452,12 +460,15 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>101</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1002</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -466,12 +477,15 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
         <v>102</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1003</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -480,12 +494,15 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
         <v>103</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1005</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -494,12 +511,15 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
         <v>104</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1004</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -508,12 +528,15 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
         <v>105</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1002</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -522,12 +545,15 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
         <v>106</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>9999</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1</v>
       </c>
     </row>

--- a/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/order_items.xlsx
+++ b/OneDrive/Documents/Exceltodb-post_data/Exceltodb-post_data/files/order_items.xlsx
@@ -413,26 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>product_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
@@ -443,15 +438,12 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="C2" t="n">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="D2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="E2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -460,15 +452,12 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="C3" t="n">
-        <v>101</v>
+        <v>1002</v>
       </c>
       <c r="D3" t="n">
-        <v>1002</v>
-      </c>
-      <c r="E3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -477,15 +466,12 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>1003</v>
       </c>
       <c r="D4" t="n">
-        <v>1003</v>
-      </c>
-      <c r="E4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -494,15 +480,12 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="C5" t="n">
-        <v>103</v>
+        <v>1005</v>
       </c>
       <c r="D5" t="n">
-        <v>1005</v>
-      </c>
-      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -511,15 +494,12 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="C6" t="n">
-        <v>104</v>
+        <v>1004</v>
       </c>
       <c r="D6" t="n">
-        <v>1004</v>
-      </c>
-      <c r="E6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -528,15 +508,12 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>105</v>
+        <v>1002</v>
       </c>
       <c r="D7" t="n">
-        <v>1002</v>
-      </c>
-      <c r="E7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -545,15 +522,12 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>106</v>
+        <v>9999</v>
       </c>
       <c r="D8" t="n">
-        <v>9999</v>
-      </c>
-      <c r="E8" t="n">
         <v>1</v>
       </c>
     </row>
